--- a/PROPEL_SCM_ROSTER_HOURS.xlsx
+++ b/PROPEL_SCM_ROSTER_HOURS.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pwc-my.sharepoint.com/personal/kuntal_pharas_pwc_com/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pwc-my.sharepoint.com/personal/kuntal_pharas_pwc_com/Documents/AI/Claude/PGE_RESOURCE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{5F27BD8E-4A8B-4771-8BD9-2D6F3C79D20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A7B7CE8-4671-4D7B-87FF-377B4C3E1381}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{5F27BD8E-4A8B-4771-8BD9-2D6F3C79D20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE7E026A-F868-41BC-878E-2AB78B6842D4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCM_R1_HOURS" sheetId="1" r:id="rId1"/>
+    <sheet name="PROPEL_TIMELINE" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SCM_R1_HOURS!$A$1:$Y$1</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="245">
   <si>
     <t>SERIAL_ID</t>
   </si>
@@ -747,6 +748,33 @@
   </si>
   <si>
     <t>SX15</t>
+  </si>
+  <si>
+    <t>PHASE</t>
+  </si>
+  <si>
+    <t>START_DT</t>
+  </si>
+  <si>
+    <t>END_DT</t>
+  </si>
+  <si>
+    <t>OVERLAP</t>
+  </si>
+  <si>
+    <t>MOBILIZATION</t>
+  </si>
+  <si>
+    <t>OVERLAP_PHASE</t>
+  </si>
+  <si>
+    <t>ENTERPRISE DESIGN</t>
+  </si>
+  <si>
+    <t>R1 DETAIL DESIGN</t>
+  </si>
+  <si>
+    <t>OVERLAP_PERIOD_IN_MONTHS</t>
   </si>
 </sst>
 </file>
@@ -756,8 +784,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -785,10 +821,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3643,7 +3681,112 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156F66E1-15C7-4130-9613-DB2B57FAA922}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45566</v>
+      </c>
+      <c r="C2" s="4">
+        <v>45716</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45717</v>
+      </c>
+      <c r="C3" s="4">
+        <v>46081</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45962</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46568</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="85d4c6ac-da51-4bd5-bea4-a68ca98bb185" xsi:nil="true"/>
+    <Notes xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c" xsi:nil="true"/>
+    <Status xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c" xsi:nil="true"/>
+    <Image xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59CEB395CDF7140B0B9D47146400687" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ed4f78c1becf1628f6d02bc8686de57b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e612708f-71dc-4c91-8d39-b6be3fd2273c" xmlns:ns3="85d4c6ac-da51-4bd5-bea4-a68ca98bb185" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5fa092d32cba1c4245e73715c590a48" ns2:_="" ns3:_="">
     <xsd:import namespace="e612708f-71dc-4c91-8d39-b6be3fd2273c"/>
@@ -3882,20 +4025,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="85d4c6ac-da51-4bd5-bea4-a68ca98bb185" xsi:nil="true"/>
-    <Notes xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c" xsi:nil="true"/>
-    <Status xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c" xsi:nil="true"/>
-    <Image xmlns="e612708f-71dc-4c91-8d39-b6be3fd2273c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3906,6 +4035,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3D8E402-0758-4B63-954E-01F7C9446812}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e612708f-71dc-4c91-8d39-b6be3fd2273c"/>
+    <ds:schemaRef ds:uri="85d4c6ac-da51-4bd5-bea4-a68ca98bb185"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEA2F9CF-2F8F-402F-835C-AE2D4A3E434B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3924,17 +4064,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3D8E402-0758-4B63-954E-01F7C9446812}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e612708f-71dc-4c91-8d39-b6be3fd2273c"/>
-    <ds:schemaRef ds:uri="85d4c6ac-da51-4bd5-bea4-a68ca98bb185"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FF0964A-3D86-4B38-9F76-81306CAE0037}">
   <ds:schemaRefs>
